--- a/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
+++ b/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
@@ -843,14 +843,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45182.57899599815</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="23">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -900,16 +896,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -1007,8 +993,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="23">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1021,34 +1005,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="23"/>
     <row r="38" ht="16.5" customHeight="1" s="23"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="23">
       <c r="A42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
+++ b/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
@@ -843,7 +843,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
+++ b/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
@@ -843,7 +843,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
+++ b/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
@@ -843,10 +843,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45266</v>
+        <v>45232.58380140895</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="23">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -896,6 +900,16 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -951,7 +965,7 @@
       </c>
       <c r="C29" s="32" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>315.2</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1" s="23">
@@ -967,7 +981,7 @@
       </c>
       <c r="C30" s="32" t="n"/>
       <c r="D30" s="16" t="n">
-        <v>334.8</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1" s="23">
@@ -983,7 +997,7 @@
       </c>
       <c r="C31" s="30" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>425.1</v>
+        <v>494</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1" s="23">
@@ -993,6 +1007,8 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="23">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1005,29 +1021,34 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="23"/>
     <row r="38" ht="16.5" customHeight="1" s="23"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="23">
       <c r="A42" s="5" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
+++ b/LISTAS/ma/FRATACHOS PLASTICOS DISMAY.xlsx
@@ -843,14 +843,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45232.58380140895</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="23">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -900,16 +896,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -965,7 +951,7 @@
       </c>
       <c r="C29" s="32" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>366</v>
+        <v>315.2</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1" s="23">
@@ -981,7 +967,7 @@
       </c>
       <c r="C30" s="32" t="n"/>
       <c r="D30" s="16" t="n">
-        <v>389</v>
+        <v>334.8</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1" s="23">
@@ -997,7 +983,7 @@
       </c>
       <c r="C31" s="30" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>494</v>
+        <v>425.1</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1" s="23">
@@ -1007,8 +993,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="23">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1021,34 +1005,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="23"/>
     <row r="38" ht="16.5" customHeight="1" s="23"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="23">
       <c r="A42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
